--- a/artfynd/A 62275-2023 artfynd.xlsx
+++ b/artfynd/A 62275-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62275-2023 artfynd.xlsx
+++ b/artfynd/A 62275-2023 artfynd.xlsx
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68086425</v>
+        <v>73185957</v>
       </c>
       <c r="B2" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>NB Gravol, väst NR Fänstjärn, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407684.2237750338</v>
+        <v>407684</v>
       </c>
       <c r="R2" t="n">
-        <v>6702278.378176042</v>
+        <v>6702278</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -747,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-09-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-09-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-08-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På murken granlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73185957</v>
+        <v>73185940</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,37 +792,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>NB Gravol, väst NR Fänstjärn, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407684.2237750338</v>
+        <v>407684</v>
       </c>
       <c r="R3" t="n">
-        <v>6702278.378176042</v>
+        <v>6702278</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -866,24 +851,14 @@
           <t>2018-08-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-08-28</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På murken granlåga.</t>
+          <t>På grov asplåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,12 +889,7 @@
         <v>73185949</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>407684.2237750338</v>
+        <v>407684</v>
       </c>
       <c r="R4" t="n">
-        <v>6702278.378176042</v>
+        <v>6702278</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -986,19 +956,9 @@
           <t>2018-08-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-08-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1031,15 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73185977</v>
+        <v>68086425</v>
       </c>
       <c r="B5" t="n">
-        <v>43464</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,47 +1002,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101735</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>NB Gravol, väst NR Fänstjärn, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>407684.2237750338</v>
+        <v>407684</v>
       </c>
       <c r="R5" t="n">
-        <v>6702278.378176042</v>
+        <v>6702278</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1114,27 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-09-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Utgångshål i fnösketicka.</t>
+          <t>2017-09-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,52 +1091,58 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73185940</v>
+        <v>73185977</v>
       </c>
       <c r="B6" t="n">
-        <v>89652</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>101735</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>NB Gravol, väst NR Fänstjärn, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>407684.2237750338</v>
+        <v>407684</v>
       </c>
       <c r="R6" t="n">
-        <v>6702278.378176042</v>
+        <v>6702278</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1237,24 +1172,14 @@
           <t>2018-08-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-08-28</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På grov asplåga.</t>
+          <t>Utgångshål i fnösketicka.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 62275-2023 artfynd.xlsx
+++ b/artfynd/A 62275-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73185957</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73185940</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73185949</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68086425</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,8 +1229,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73185977</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>